--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486279_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486279_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4495</v>
+        <v>2.3966</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6294</v>
+        <v>5.145</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.1799</v>
+        <v>-2.7484</v>
       </c>
       <c r="G2" t="n">
         <v>3.5792</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3923</v>
+        <v>-0.4452</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0839</v>
+        <v>-0.5684</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3084</v>
+        <v>0.1232</v>
       </c>
       <c r="V2" t="n">
         <v>-2.2599</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3351</v>
+        <v>1.9932</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4668</v>
+        <v>3.0941</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1317</v>
+        <v>-1.1009</v>
       </c>
       <c r="G3" t="n">
         <v>-0.8889</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.341</v>
+        <v>-0.6829</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0034</v>
+        <v>-0.3761</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3376</v>
+        <v>-0.3067</v>
       </c>
       <c r="V3" t="n">
         <v>2.2599</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ZIDEK</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0106</v>
+        <v>1.7931</v>
       </c>
       <c r="E4" t="n">
-        <v>1.18</v>
+        <v>3.2829</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1694</v>
+        <v>-1.4898</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4181</v>
+        <v>-1.3148</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0698</v>
+        <v>-0.0303</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3482</v>
+        <v>-1.2845</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5719</v>
+        <v>-0.878</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0547</v>
+        <v>0.5356</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5172</v>
+        <v>-1.4136</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1539</v>
+        <v>-0.4368</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0151</v>
+        <v>-0.5659</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1689</v>
+        <v>0.1291</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>0.375</v>
+        <v>-0.1742</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6081</v>
+        <v>0.0108</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.233</v>
+        <v>-0.1851</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.6297</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.1501</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9878</v>
+        <v>1.3877</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7241</v>
+        <v>2.3567</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7364</v>
+        <v>-0.969</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3148</v>
+        <v>-1.0118</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0303</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2845</v>
+        <v>-1.079</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.878</v>
+        <v>0.6219</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5356</v>
+        <v>1.214</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4136</v>
+        <v>-0.5921</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4368</v>
+        <v>-1.6337</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5659</v>
+        <v>-1.1468</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1291</v>
+        <v>-0.4869</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9796</v>
+        <v>-0.0354</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.548</v>
+        <v>-0.5251</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4317</v>
+        <v>0.4897</v>
       </c>
       <c r="V5" t="n">
-        <v>2.6297</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>4.1501</v>
+        <v>2.2599</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5204</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>J. ZIDEK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6988</v>
+        <v>0.5944</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7294</v>
+        <v>0.733</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0306</v>
+        <v>-0.1385</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0118</v>
+        <v>0.4181</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0698</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.079</v>
+        <v>0.3482</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6219</v>
+        <v>0.5719</v>
       </c>
       <c r="K6" t="n">
-        <v>1.214</v>
+        <v>0.0547</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5921</v>
+        <v>0.5172</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6337</v>
+        <v>-0.1539</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1468</v>
+        <v>0.0151</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4869</v>
+        <v>-0.1689</v>
       </c>
       <c r="P6" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7244</v>
+        <v>-0.0412</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1524</v>
+        <v>0.161</v>
       </c>
       <c r="U6" t="n">
-        <v>0.428</v>
+        <v>-0.2022</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>A. ALONSO RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3821</v>
+        <v>0.1988</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7798</v>
+        <v>1.131</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3977</v>
+        <v>-0.9322</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1305</v>
+        <v>1.1537</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3225</v>
+        <v>-1.0464</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8081</v>
+        <v>2.2001</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2959</v>
+        <v>2.3875</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1743</v>
+        <v>0.1674</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4702</v>
+        <v>2.2201</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8346</v>
+        <v>-1.2337</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4967</v>
+        <v>-1.2138</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3379</v>
+        <v>-0.0199</v>
       </c>
       <c r="P7" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2076</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9458</v>
+        <v>-0.7547</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2618</v>
+        <v>0.1694</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0.5857</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ALONSO RUIZ</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4199</v>
+        <v>-0.8095</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8822</v>
+        <v>0.619</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3021</v>
+        <v>-1.4285</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1537</v>
+        <v>-2.1305</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0464</v>
+        <v>-0.3225</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2001</v>
+        <v>-1.8081</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3875</v>
+        <v>-0.2959</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1674</v>
+        <v>1.1743</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2201</v>
+        <v>-1.4702</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2337</v>
+        <v>-1.8346</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2138</v>
+        <v>-1.4967</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0199</v>
+        <v>-0.3379</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2039</v>
+        <v>0.0159</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0034</v>
+        <v>-0.2151</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2004</v>
+        <v>0.231</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5857</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9554</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8744</v>
+        <v>-1.0024</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3215</v>
+        <v>-0.1413</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.8611</v>
       </c>
       <c r="G9" t="n">
         <v>0.4356</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.31</v>
+        <v>-0.438</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.536</v>
+        <v>-0.3557</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2259</v>
+        <v>-0.0823</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5649999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2861</v>
+        <v>-1.1242</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3051</v>
+        <v>-1.0816</v>
       </c>
       <c r="F10" t="n">
-        <v>0.019</v>
+        <v>-0.0426</v>
       </c>
       <c r="G10" t="n">
         <v>0.6476</v>
@@ -1234,13 +1234,13 @@
         <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6732</v>
+        <v>-0.5113</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.274</v>
+        <v>-0.0505</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3992</v>
+        <v>-0.4609</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3904</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3366</v>
+        <v>-1.6697</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8979</v>
+        <v>-2.9844</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5613</v>
+        <v>1.3147</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1482</v>
@@ -1312,13 +1312,13 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4059</v>
+        <v>-0.739</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2704</v>
+        <v>-0.3569</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1356</v>
+        <v>-0.3822</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.649</v>
+        <v>-8.7751</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5204</v>
+        <v>-6.1225</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1286</v>
+        <v>-2.6526</v>
       </c>
       <c r="G12" t="n">
         <v>-6.1752</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9627</v>
+        <v>0.8367</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4062</v>
+        <v>-0.1959</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5565</v>
+        <v>1.0325</v>
       </c>
       <c r="V12" t="n">
         <v>-1.479</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.7021</v>
+        <v>-5.0171</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3468</v>
+        <v>6.031900000000003</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.049</v>
+        <v>-11.0489</v>
       </c>
       <c r="G13" t="n">
         <v>-6.4352</v>
@@ -1444,10 +1444,10 @@
         <v>4.009600000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>3.833900000000001</v>
+        <v>3.8339</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1755000000000004</v>
+        <v>0.1754999999999995</v>
       </c>
       <c r="M13" t="n">
         <v>-10.4446</v>
@@ -1468,13 +1468,13 @@
         <v>10.875</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.485</v>
+        <v>-2.799799999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.9114</v>
+        <v>-3.2266</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4262999999999999</v>
+        <v>0.4264000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.9554999999999998</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.8795</v>
+        <v>9.6747</v>
       </c>
       <c r="E14" t="n">
-        <v>8.6327</v>
+        <v>9.1915</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2468</v>
+        <v>0.4832</v>
       </c>
       <c r="G14" t="n">
         <v>7.5172</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1043</v>
+        <v>0.8995</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0034</v>
+        <v>-0.4446</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1077</v>
+        <v>1.3441</v>
       </c>
       <c r="V14" t="n">
         <v>3.4331</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9177</v>
+        <v>4.0589</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9132</v>
+        <v>4.6897</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9956</v>
+        <v>-0.6308</v>
       </c>
       <c r="G15" t="n">
         <v>2.9723</v>
@@ -1624,13 +1624,13 @@
         <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5104</v>
+        <v>0.6516</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2896</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2207</v>
+        <v>0.5855</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8179</v>
+        <v>3.2861</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7336</v>
+        <v>3.5101</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0843</v>
+        <v>-0.224</v>
       </c>
       <c r="G16" t="n">
         <v>2.0339</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9145</v>
+        <v>0.3827</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0036</v>
+        <v>-0.2199</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9109</v>
+        <v>0.6026</v>
       </c>
       <c r="V16" t="n">
         <v>1.3045</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4676</v>
+        <v>0.4984</v>
       </c>
       <c r="E17" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5361</v>
+        <v>0.5669</v>
       </c>
       <c r="G17" t="n">
         <v>0.298</v>
@@ -1780,13 +1780,13 @@
         <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0479</v>
+        <v>-0.0171</v>
       </c>
       <c r="T17" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8278</v>
+        <v>0.0456</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4153</v>
+        <v>0.0317</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4125</v>
+        <v>0.0139</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1276</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5926</v>
+        <v>0.2809</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6609</v>
+        <v>-0.2139</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0684</v>
+        <v>0.4948</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1952</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>P. RIGOT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1858</v>
+        <v>-1.1648</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6428</v>
+        <v>-2.4091</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5431</v>
+        <v>1.2443</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8223</v>
+        <v>-2.4338</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5897</v>
+        <v>0.2038</v>
       </c>
       <c r="I19" t="n">
-        <v>1.412</v>
+        <v>-2.6376</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0679</v>
+        <v>-3.1381</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3412</v>
+        <v>0.5871</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7267</v>
+        <v>-3.7253</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2456</v>
+        <v>0.7043</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.3834</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6853</v>
+        <v>1.0877</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.8276</v>
+        <v>-0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4801</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9063</v>
+        <v>0.7261</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5742</v>
+        <v>-0.2259</v>
       </c>
       <c r="U19" t="n">
-        <v>0.332</v>
+        <v>0.952</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0868</v>
+        <v>0.9779</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>2.2599</v>
       </c>
       <c r="X19" t="n">
         <v>-1.282</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6634</v>
+        <v>-1.5028</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1418</v>
+        <v>-0.2536</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5215</v>
+        <v>-1.2492</v>
       </c>
       <c r="G20" t="n">
         <v>0.6936</v>
@@ -2014,13 +2014,13 @@
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0548</v>
+        <v>0.1057</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0721</v>
+        <v>-0.0396</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1269</v>
+        <v>0.1454</v>
       </c>
       <c r="V20" t="n">
         <v>-3.1722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. RIGOT</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7557</v>
+        <v>-2.0247</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8562</v>
+        <v>-1.8721</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1004</v>
+        <v>-0.1526</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4338</v>
+        <v>0.8223</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2038</v>
+        <v>-0.5897</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6376</v>
+        <v>1.412</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1381</v>
+        <v>1.0679</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5871</v>
+        <v>0.3412</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.7253</v>
+        <v>0.7267</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7043</v>
+        <v>-0.2456</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3834</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0877</v>
+        <v>0.6853</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.435</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.305</v>
+        <v>-3.4801</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1352</v>
+        <v>1.0674</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.3449</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8081</v>
+        <v>0.7225</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9779</v>
+        <v>-1.0868</v>
       </c>
       <c r="W21" t="n">
-        <v>2.2599</v>
+        <v>0.1952</v>
       </c>
       <c r="X21" t="n">
         <v>-1.282</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4545</v>
+        <v>-2.5547</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7285</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7259</v>
+        <v>-1.6026</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5335</v>
@@ -2170,13 +2170,13 @@
         <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6218</v>
+        <v>0.5215</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6886</v>
+        <v>0.4651</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0668</v>
+        <v>0.0565</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7602</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4934</v>
+        <v>-3.1246</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3776</v>
+        <v>-0.8188</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1158</v>
+        <v>-2.3058</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8072</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0121</v>
+        <v>0.3566</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6489</v>
+        <v>-0.0901</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6368</v>
+        <v>0.4467</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4566</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.7021</v>
+        <v>7.192100000000001</v>
       </c>
       <c r="E24" t="n">
         <v>11.0488</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.3468</v>
+        <v>-3.8567</v>
       </c>
       <c r="G24" t="n">
         <v>6.4352</v>
@@ -2305,7 +2305,7 @@
         <v>8.6556</v>
       </c>
       <c r="L24" t="n">
-        <v>1.789</v>
+        <v>1.789000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-4.0095</v>
@@ -2323,16 +2323,16 @@
         <v>-10.8752</v>
       </c>
       <c r="R24" t="n">
-        <v>7.6125</v>
+        <v>7.612500000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4851</v>
+        <v>4.974899999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4265</v>
+        <v>-0.4264000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>3.9114</v>
+        <v>5.4015</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9554999999999996</v>
